--- a/Report_Nhom_214.xlsx
+++ b/Report_Nhom_214.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\C#\Nhom_214_Selenium_Test\Nhom_214\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\214_Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB918089-1465-4E84-94FF-2FD1A0184CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Voucher" sheetId="7" r:id="rId1"/>
@@ -519,7 +518,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -922,25 +921,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -978,7 +977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -1014,7 +1013,7 @@
       </c>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -1050,7 +1049,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -1076,7 +1075,7 @@
       </c>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -1104,22 +1103,22 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1145,7 +1144,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
@@ -1169,7 +1168,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>45</v>
       </c>
@@ -1199,7 +1198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>48</v>
       </c>
@@ -1219,7 +1218,7 @@
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>50</v>
       </c>
@@ -1241,7 +1240,7 @@
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>52</v>
       </c>
@@ -1264,7 +1263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>56</v>
       </c>
@@ -1287,7 +1286,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>60</v>
       </c>
@@ -1317,15 +1316,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="9.109375" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="1" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1360,7 +1359,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>67</v>
       </c>
@@ -1391,7 +1390,7 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>73</v>
       </c>
@@ -1422,7 +1421,7 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>76</v>
       </c>
@@ -1455,7 +1454,7 @@
       </c>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>81</v>
       </c>
@@ -1488,7 +1487,7 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>86</v>
       </c>
@@ -1521,7 +1520,7 @@
       </c>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>90</v>
       </c>
@@ -1554,7 +1553,7 @@
       </c>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>93</v>
       </c>
@@ -1587,7 +1586,7 @@
       </c>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>98</v>
       </c>
@@ -1626,17 +1625,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18D1926A-EA42-44D4-8C92-D81B9617D533}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1668,7 +1667,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>108</v>
       </c>
@@ -1700,7 +1699,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>115</v>
       </c>
@@ -1732,7 +1731,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>119</v>
       </c>
@@ -1766,31 +1765,31 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
-    <hyperlink ref="J4" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
-    <hyperlink ref="F4" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
+    <hyperlink ref="J2" r:id="rId1"/>
+    <hyperlink ref="J3" r:id="rId2"/>
+    <hyperlink ref="J4" r:id="rId3"/>
+    <hyperlink ref="F4" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.109375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="155.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="155.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1825,7 +1824,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>130</v>
       </c>
@@ -1854,7 +1853,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="80.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>133</v>
       </c>
@@ -1887,7 +1886,7 @@
       </c>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="1:12" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="80.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>140</v>
       </c>
@@ -1923,7 +1922,7 @@
       </c>
       <c r="L4" s="10"/>
     </row>
-    <row r="5" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>142</v>
       </c>
@@ -1949,7 +1948,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>145</v>
       </c>
@@ -1977,7 +1976,7 @@
       </c>
       <c r="L6" s="10"/>
     </row>
-    <row r="7" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>147</v>
       </c>
@@ -2006,19 +2005,19 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K4" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="K5" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="K4" r:id="rId1"/>
+    <hyperlink ref="K5" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2041,7 +2040,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>150</v>
       </c>
@@ -2062,7 +2061,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>153</v>
       </c>
@@ -2083,7 +2082,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>156</v>
       </c>
@@ -2106,7 +2105,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>159</v>
       </c>
@@ -2127,7 +2126,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G4" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="G4" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
